--- a/data/trans_orig/P33B_R4-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R4-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>53151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>49313</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>69656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>110788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374034</t>
+          <t>376778</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352387</t>
+          <t>354642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387738</t>
+          <t>390609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>274690</t>
+          <t>313199</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257227</t>
+          <t>292856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289273</t>
+          <t>330296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>648724</t>
+          <t>689977</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>622879</t>
+          <t>659517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>669537</t>
+          <t>712398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34752</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63229</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37273</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83409</t>
+          <t>87935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>97981</t>
+          <t>107391</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74121</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124998</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>388795</t>
+          <t>436765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371485</t>
+          <t>418683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400599</t>
+          <t>450413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>448275</t>
+          <t>433816</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428095</t>
+          <t>413148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474231</t>
+          <t>447230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>837070</t>
+          <t>870582</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810053</t>
+          <t>846888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>860930</t>
+          <t>892063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>60925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88090</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90391</t>
+          <t>107548</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76011</t>
+          <t>92643</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>125440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>161536</t>
+          <t>185490</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139075</t>
+          <t>162698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184350</t>
+          <t>210963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>463209</t>
+          <t>540929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446263</t>
+          <t>522821</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478721</t>
+          <t>557946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>452077</t>
+          <t>514591</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437380</t>
+          <t>496699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466457</t>
+          <t>529496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>915285</t>
+          <t>1055520</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>892471</t>
+          <t>1030047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937746</t>
+          <t>1078312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>534353</t>
+          <t>618871</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076821</t>
+          <t>1241010</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87488</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130127</t>
+          <t>113823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>158837</t>
+          <t>168626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130709</t>
+          <t>149537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178544</t>
+          <t>187498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>246325</t>
+          <t>264170</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151236</t>
+          <t>238420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304368</t>
+          <t>290490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>800298</t>
+          <t>605073</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>757659</t>
+          <t>586794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>850009</t>
+          <t>622513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>553661</t>
+          <t>567869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>533954</t>
+          <t>548997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581789</t>
+          <t>586958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1353960</t>
+          <t>1172942</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1295917</t>
+          <t>1146622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1449049</t>
+          <t>1198692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91621</t>
+          <t>96945</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>81878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107455</t>
+          <t>113752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>162587</t>
+          <t>182811</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146731</t>
+          <t>165824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179487</t>
+          <t>199833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>254208</t>
+          <t>279755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231345</t>
+          <t>255942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276503</t>
+          <t>304657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>468583</t>
+          <t>511320</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452749</t>
+          <t>494513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484082</t>
+          <t>526387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>382979</t>
+          <t>425322</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366079</t>
+          <t>408300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398835</t>
+          <t>442309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>851562</t>
+          <t>936642</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>829267</t>
+          <t>911740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>874425</t>
+          <t>960455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58679</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>53143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>77856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>114732</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165322</t>
+          <t>128071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>179614</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86935</t>
+          <t>161842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213375</t>
+          <t>198433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>309486</t>
+          <t>342199</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298847</t>
+          <t>329224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>320291</t>
+          <t>353937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>504182</t>
+          <t>324434</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>443046</t>
+          <t>311095</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>559604</t>
+          <t>337667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>813669</t>
+          <t>666632</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>763158</t>
+          <t>647813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>889598</t>
+          <t>684404</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>73170</t>
+          <t>81398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61092</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83961</t>
+          <t>94407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>150391</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120113</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147852</t>
+          <t>165145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>208385</t>
+          <t>231789</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190998</t>
+          <t>213302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227324</t>
+          <t>250269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>209589</t>
+          <t>228800</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198798</t>
+          <t>215791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>221667</t>
+          <t>241254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>289563</t>
+          <t>313062</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276926</t>
+          <t>298308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>304665</t>
+          <t>327790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>499152</t>
+          <t>541863</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480213</t>
+          <t>523383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>516539</t>
+          <t>560350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424778</t>
+          <t>463453</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707537</t>
+          <t>773652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>340557</t>
+          <t>447367</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>491671</t>
+          <t>536492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>798390</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>825994</t>
+          <t>882710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1026657</t>
+          <t>1270891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1294178</t>
+          <t>1389085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3013995</t>
+          <t>3041864</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2965131</t>
+          <t>2993222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3116245</t>
+          <t>3082347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2905426</t>
+          <t>2892294</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2832387</t>
+          <t>2850272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3039111</t>
+          <t>2934592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5919422</t>
+          <t>5934158</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5821006</t>
+          <t>5873611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6088527</t>
+          <t>5991805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
